--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.5216427559571</v>
+        <v>9.834766947843029</v>
       </c>
       <c r="D2" t="n">
-        <v>60.5359706390188</v>
+        <v>9.837095228840555</v>
       </c>
       <c r="E2" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F2" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.42692914204221</v>
+        <v>9.981875985581858</v>
       </c>
       <c r="D3" t="n">
-        <v>61.5944979117313</v>
+        <v>10.00910591065634</v>
       </c>
       <c r="E3" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F3" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.73795915563124</v>
+        <v>8.894918362790076</v>
       </c>
       <c r="D4" t="n">
-        <v>54.63723492460583</v>
+        <v>8.878550675248448</v>
       </c>
       <c r="E4" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F4" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.35845798632558</v>
+        <v>7.858249422777907</v>
       </c>
       <c r="D5" t="n">
-        <v>48.10228213042795</v>
+        <v>7.816620846194542</v>
       </c>
       <c r="E5" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F5" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.02368337560045</v>
+        <v>7.803848548535073</v>
       </c>
       <c r="D6" t="n">
-        <v>47.63132388865294</v>
+        <v>7.740090131906103</v>
       </c>
       <c r="E6" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F6" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.12450975849721</v>
+        <v>5.057732835755797</v>
       </c>
       <c r="D7" t="n">
-        <v>31.21294112817476</v>
+        <v>5.072102933328398</v>
       </c>
       <c r="E7" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F7" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.68904352284059</v>
+        <v>4.174469572461596</v>
       </c>
       <c r="D8" t="n">
-        <v>25.59338394510353</v>
+        <v>4.158924891079324</v>
       </c>
       <c r="E8" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F8" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.03477906148096</v>
+        <v>4.718151597490657</v>
       </c>
       <c r="D9" t="n">
-        <v>28.5373178807978</v>
+        <v>4.637314155629642</v>
       </c>
       <c r="E9" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F9" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.04383777820489</v>
+        <v>5.857123638958295</v>
       </c>
       <c r="D10" t="n">
-        <v>37.47994295351402</v>
+        <v>6.090490729946028</v>
       </c>
       <c r="E10" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F10" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.65630335119346</v>
+        <v>2.544149294568937</v>
       </c>
       <c r="D11" t="n">
-        <v>15.13048147901247</v>
+        <v>2.458703240339527</v>
       </c>
       <c r="E11" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F11" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.67498503733808</v>
+        <v>3.197185068567439</v>
       </c>
       <c r="D12" t="n">
-        <v>21.3188668444409</v>
+        <v>3.464315862221647</v>
       </c>
       <c r="E12" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F12" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.84044037074815</v>
+        <v>5.499071560246574</v>
       </c>
       <c r="D13" t="n">
-        <v>34.15900424691558</v>
+        <v>5.550838190123782</v>
       </c>
       <c r="E13" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F13" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.9851464769859</v>
+        <v>5.685086302510208</v>
       </c>
       <c r="D14" t="n">
-        <v>35.172778581516</v>
+        <v>5.71557651949635</v>
       </c>
       <c r="E14" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F14" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.09471909673086</v>
+        <v>6.840391853218765</v>
       </c>
       <c r="D15" t="n">
-        <v>30.07701235221807</v>
+        <v>4.887514507235436</v>
       </c>
       <c r="E15" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F15" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.9282392914567</v>
+        <v>1.613338884861714</v>
       </c>
       <c r="D16" t="n">
-        <v>12.30149692044364</v>
+        <v>1.998993249572091</v>
       </c>
       <c r="E16" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F16" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>56.13571417092748</v>
+        <v>9.122053552775716</v>
       </c>
       <c r="D17" t="n">
-        <v>28.26586228389208</v>
+        <v>4.593202621132463</v>
       </c>
       <c r="E17" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F17" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>24.40283986075085</v>
+        <v>3.965461477372014</v>
       </c>
       <c r="D18" t="n">
-        <v>22.20485429752662</v>
+        <v>3.608288823348076</v>
       </c>
       <c r="E18" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F18" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>62.22958106926271</v>
+        <v>10.11230692375519</v>
       </c>
       <c r="D19" t="n">
-        <v>29.55650608840962</v>
+        <v>4.802932239366563</v>
       </c>
       <c r="E19" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F19" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.83379090143467</v>
+        <v>3.222991021483133</v>
       </c>
       <c r="D20" t="n">
-        <v>19.38972175072814</v>
+        <v>3.150829784493323</v>
       </c>
       <c r="E20" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F20" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>31.17274277321136</v>
+        <v>5.065570700646847</v>
       </c>
       <c r="D21" t="n">
-        <v>9.003328261865331</v>
+        <v>1.463040842553116</v>
       </c>
       <c r="E21" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F21" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>57.98138790813434</v>
+        <v>9.421975535071832</v>
       </c>
       <c r="D22" t="n">
-        <v>56.00749301265878</v>
+        <v>9.101217614557052</v>
       </c>
       <c r="E22" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F22" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>62.04976743073243</v>
+        <v>10.08308720749402</v>
       </c>
       <c r="D23" t="n">
-        <v>62.19343103912991</v>
+        <v>10.10643254385861</v>
       </c>
       <c r="E23" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F23" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>24.02991372419437</v>
+        <v>3.904860980181586</v>
       </c>
       <c r="D24" t="n">
-        <v>23.56876867106329</v>
+        <v>3.829924909047785</v>
       </c>
       <c r="E24" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F24" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>28.13858362403053</v>
+        <v>4.572519838904961</v>
       </c>
       <c r="D25" t="n">
-        <v>18.27837402276526</v>
+        <v>2.970235778699355</v>
       </c>
       <c r="E25" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F25" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>31.90097478828467</v>
+        <v>5.18390840309626</v>
       </c>
       <c r="D26" t="n">
-        <v>30.99541283975965</v>
+        <v>5.036754586460943</v>
       </c>
       <c r="E26" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F26" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>47.16393031014272</v>
+        <v>7.664138675398192</v>
       </c>
       <c r="D27" t="n">
-        <v>5.939377330480207</v>
+        <v>0.9651488162030337</v>
       </c>
       <c r="E27" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F27" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>54.38556354189026</v>
+        <v>8.837654075557168</v>
       </c>
       <c r="D28" t="n">
-        <v>18.26950829789567</v>
+        <v>2.968795098408046</v>
       </c>
       <c r="E28" t="n">
-        <v>15.64429976854566</v>
+        <v>2.54219871238867</v>
       </c>
       <c r="F28" t="n">
-        <v>16.11811695306737</v>
+        <v>2.619194004873449</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
